--- a/data/file_generation/input/data_209/2025-2026学年上学期八年级学生名单.xlsx
+++ b/data/file_generation/input/data_209/2025-2026学年上学期八年级学生名单.xlsx
@@ -7285,18 +7285,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{945D92A4-A585-471A-88A6-D4550221F53F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90F030BA-69D0-4443-93A7-0F1A80815544}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D237AD8-F366-41CA-B309-9AD14C0C1882}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D92E1A2-D366-4837-B8A1-84F371C2BAE4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D5433A3-F313-4166-91D5-7EC6371BA12C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94A641BA-F11C-481D-AB8E-CCE450E4BEA4}"/>
 </file>